--- a/frontend/public/catalogs/IOCL_Refinery_Inventory_2026.xlsx
+++ b/frontend/public/catalogs/IOCL_Refinery_Inventory_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Material Catalog" sheetId="1" r:id="rId1"/>
+    <sheet name="IOCL_Materials" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,110 +421,110 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>IOCL-P-106B-06</v>
+        <v>IOCL-TX-DP-250-HART</v>
       </c>
       <c r="B2" t="str">
-        <v>Pipe Carbon Steel Seamless 6in Sch 40 to ASTM A106 Gr.B Beveled Ends</v>
+        <v>Smart D/P Transmitter 0 to 250mbar 4-20 mA with HART Protocol Hastelloy C276 Wetted Parts 1/2" NPT</v>
       </c>
       <c r="C2" t="str">
-        <v>Pipes</v>
+        <v>Instrumentation</v>
       </c>
       <c r="D2" t="str">
-        <v>Mtr</v>
+        <v>Nos</v>
       </c>
       <c r="E2">
-        <v>4880</v>
+        <v>79200</v>
       </c>
       <c r="F2">
-        <v>14000</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>IOCL-P-106B-04</v>
+        <v>IOCL-V-BF-8IN-150L</v>
       </c>
       <c r="B3" t="str">
-        <v>CS Seamless Pipe 4 Inch NB Schedule 40 Grade B ASTM A106</v>
+        <v>Butterfly Valve 8 Inch 150 LB Triple Eccentric Lugged CS Body Disc CF8M / SS316 Fire Safe API 609 with Gearbox</v>
       </c>
       <c r="C3" t="str">
-        <v>Pipes</v>
+        <v>Valves</v>
       </c>
       <c r="D3" t="str">
-        <v>Mtr</v>
+        <v>Nos</v>
       </c>
       <c r="E3">
-        <v>3220</v>
+        <v>65200</v>
       </c>
       <c r="F3">
-        <v>9000</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>IOCL-P-SS316-02</v>
+        <v>IOCL-FM-CORIOLIS-2IN</v>
       </c>
       <c r="B4" t="str">
-        <v>Seamless Pipe SS316L 2 Inch Sch 40S ASTM A312 TP316L</v>
+        <v>Mass Flowmeter Coriolis Type 2 Inch 300 LB Flanged Measuring Range 50000 kg/h SS316L Sensor 4-20mA HART Output</v>
       </c>
       <c r="C4" t="str">
-        <v>Pipes</v>
+        <v>Instrumentation</v>
       </c>
       <c r="D4" t="str">
-        <v>Mtr</v>
+        <v>Nos</v>
       </c>
       <c r="E4">
-        <v>8920</v>
+        <v>325000</v>
       </c>
       <c r="F4">
-        <v>5100</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>IOCL-V-300-FB04</v>
+        <v>IOCL-P-A333-8S80</v>
       </c>
       <c r="B5" t="str">
-        <v>Ball Valve 4in 300 LB WCB Body CS Flanged Trim SS316 Fire Safe API 6D</v>
+        <v>Seamless Pipe Low Temperature CS 8 Inch NB Schedule 80 to ASTM A333 Gr 6 Beveled End</v>
       </c>
       <c r="C5" t="str">
-        <v>Valves</v>
+        <v>Pipes</v>
       </c>
       <c r="D5" t="str">
-        <v>Nos</v>
+        <v>Mtr</v>
       </c>
       <c r="E5">
-        <v>24700</v>
+        <v>14350</v>
       </c>
       <c r="F5">
-        <v>520</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>IOCL-V-150-GT06</v>
+        <v>IOCL-TEMP-RTD-DUAL</v>
       </c>
       <c r="B6" t="str">
-        <v>Gate Valve 6in 150 LB Flanged WCB Carbon Steel Trim 8 Handwheel Operated API 600</v>
+        <v>Dual Element RTD Pt 100 3-Wire Duplex Class A Immersion Length 400mm with Barstock Thermowell 1.5" 300 LB RF SS316</v>
       </c>
       <c r="C6" t="str">
-        <v>Valves</v>
+        <v>Instrumentation</v>
       </c>
       <c r="D6" t="str">
         <v>Nos</v>
       </c>
       <c r="E6">
-        <v>38200</v>
+        <v>12700</v>
       </c>
       <c r="F6">
-        <v>410</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>IOCL-V-300-CK03</v>
+        <v>IOCL-V-NDL-12NPT-6K</v>
       </c>
       <c r="B7" t="str">
-        <v>Check Valve 3in Class 300 Swing Type Flanged WCB Carbon Steel API 6D</v>
+        <v>Instrument Needle Valve 1/2 Inch FNPT 6000 LB WOG Forged SS316 Bar Stock Body Screwed Bonnet</v>
       </c>
       <c r="C7" t="str">
         <v>Valves</v>
@@ -533,135 +533,295 @@
         <v>Nos</v>
       </c>
       <c r="E7">
-        <v>16600</v>
+        <v>4350</v>
       </c>
       <c r="F7">
-        <v>310</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>IOCL-F-B7-20X12</v>
+        <v>IOCL-FL-BLIND-8-300</v>
       </c>
       <c r="B8" t="str">
-        <v>Stud Bolt with 2 Heavy Hex Nuts M20x120 Alloy Steel ASTM A193 B7 / A194 2H</v>
+        <v>Spectacle Blind 8 Inch 300 LB RF to ASME B16.48 Material CS ASTM A516 Grade 70</v>
       </c>
       <c r="C8" t="str">
-        <v>Fasteners</v>
+        <v>Fittings</v>
       </c>
       <c r="D8" t="str">
-        <v>Set</v>
+        <v>Nos</v>
       </c>
       <c r="E8">
-        <v>345</v>
+        <v>8600</v>
       </c>
       <c r="F8">
-        <v>28000</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>IOCL-F-B7-24X16</v>
+        <v>IOCL-GK-RTJ-R45</v>
       </c>
       <c r="B9" t="str">
-        <v>Stud Bolt with 2 Nuts M24x160mm Long ASTM A193 B7 / A194 2H Black Finish</v>
+        <v>Ring Type Joint Gasket Size R-45 Octagonal Profile Soft Iron Material for API 6A / ASME B16.5 Flanges</v>
       </c>
       <c r="C9" t="str">
-        <v>Fasteners</v>
+        <v>Fittings</v>
       </c>
       <c r="D9" t="str">
-        <v>Set</v>
+        <v>Nos</v>
       </c>
       <c r="E9">
-        <v>525</v>
+        <v>1920</v>
       </c>
       <c r="F9">
-        <v>21000</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>IOCL-FL-WN-300-6</v>
+        <v>IOCL-E-FLD-200-EXD</v>
       </c>
       <c r="B10" t="str">
-        <v>Flange Weld Neck 6in 300 LB RF CS A105 ASME B16.5 Sch 40 Bore</v>
+        <v>Flameproof LED Flood Light Fitting 200 Watt 240V AC Gas Group IIC Zone 1 &amp; 2 IP66 Corrosion Resistant LM6</v>
       </c>
       <c r="C10" t="str">
-        <v>Fittings</v>
+        <v>Electrical</v>
       </c>
       <c r="D10" t="str">
         <v>Nos</v>
       </c>
       <c r="E10">
-        <v>6220</v>
+        <v>35200</v>
       </c>
       <c r="F10">
-        <v>1350</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>IOCL-GK-SP-300-6</v>
+        <v>IOCL-S-DET-4GAS-PMP</v>
       </c>
       <c r="B11" t="str">
-        <v>Metallic Gasket Spiral Wound 6in 300 LB SS316 Graphite Filler ASME B16.20</v>
+        <v>Multi Gas Monitor 4-Gas Oxygen Combustible LEL Hydrogen Sulfide Carbon Monoxide with Built-in Motorized Pump Intrinsically Safe</v>
       </c>
       <c r="C11" t="str">
-        <v>Fittings</v>
+        <v>Safety</v>
       </c>
       <c r="D11" t="str">
         <v>Nos</v>
       </c>
       <c r="E11">
-        <v>455</v>
+        <v>57500</v>
       </c>
       <c r="F11">
-        <v>16000</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>IOCL-S-HLM-WHT</v>
+        <v>IOCL-S-SCBA-300B-68</v>
       </c>
       <c r="B12" t="str">
-        <v>Industrial Safety Helmet White HDPE Shell Ratchet Suspension IS 2925</v>
+        <v>SCBA Breathing Apparatus Set with 6.8L 300 Bar Composite Carbon Cylinder Positive Pressure Facepiece to EN 137 Class II</v>
       </c>
       <c r="C12" t="str">
         <v>Safety</v>
       </c>
       <c r="D12" t="str">
-        <v>Nos</v>
+        <v>Set</v>
       </c>
       <c r="E12">
-        <v>485</v>
+        <v>83500</v>
       </c>
       <c r="F12">
-        <v>7500</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>IOCL-E-FL-60W</v>
+        <v>IOCL-V-DP-CHK-6-300</v>
       </c>
       <c r="B13" t="str">
-        <v>Flameproof LED Fitting 60 Watt 240V AC Ex d IIC T6 IP66 Wellhead / Refinery</v>
+        <v>Dual Plate Wafer Check Valve 6 Inch 300 LB Body and Discs Duplex SS S31803 Retainerless Design API 594</v>
       </c>
       <c r="C13" t="str">
-        <v>Electrical</v>
+        <v>Valves</v>
       </c>
       <c r="D13" t="str">
         <v>Nos</v>
       </c>
       <c r="E13">
-        <v>18600</v>
+        <v>53400</v>
       </c>
       <c r="F13">
-        <v>920</v>
+        <v>130</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>IOCL-T-A213-T22-2IN</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Alloy Steel Boiler Tube 2" OD x 4.5mm WT Seamless to ASTM A213 Gr. T22 Hydrotested</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Pipes</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Mtr</v>
+      </c>
+      <c r="E14">
+        <v>3920</v>
+      </c>
+      <c r="F14">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>IOCL-M-BRG-6312-2Z</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Single Row Radial Ball Bearing 6312-2Z / C3 Metal Shields 60x130x31mm Motor &amp; Pump Application</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Nos</v>
+      </c>
+      <c r="E15">
+        <v>3180</v>
+      </c>
+      <c r="F15">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>IOCL-REF-CAT-HYD-50</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Hydrocracking Catalyst Nickel Molybdenum on Alumina Extrudates 1.3mm Bulk Density 0.75 g/ml</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Catalysts</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Kg</v>
+      </c>
+      <c r="E16">
+        <v>1850</v>
+      </c>
+      <c r="F16">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>IOCL-REF-FURN-TUB-HP</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Ethylene Cracking Furnace Radiating Coil Tube HP-40 Nb Modified Alloy 25Cr-35Ni</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Pipes</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Mtr</v>
+      </c>
+      <c r="E17">
+        <v>48000</v>
+      </c>
+      <c r="F17">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>IOCL-PMP-CRU-SUL-BB2</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Heavy Crude Column Bottoms Pump API 610 BB2 Between Bearing 8x6x13 Duplex Impeller</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Nos</v>
+      </c>
+      <c r="E18">
+        <v>1850000</v>
+      </c>
+      <c r="F18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>IOCL-COL-TR-VAL-SS</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Heavy Duty High-Capacity Valve Tray Cap SS410 for Distillation Fractionator Column</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Vessels</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Nos</v>
+      </c>
+      <c r="E19">
+        <v>750</v>
+      </c>
+      <c r="F19">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>IOCL-INST-GAS-CHRO</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Online Process Gas Chromatograph Explosion Proof C1-C6 Analysis with Sample System</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Instrumentation</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Nos</v>
+      </c>
+      <c r="E20">
+        <v>1650000</v>
+      </c>
+      <c r="F20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>IOCL-REF-EXP-TURB-01</v>
+      </c>
+      <c r="B21" t="str">
+        <v>FCC Flue Gas Power Recovery Expander Turbine Rotor Inconel 738LC Blading</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Turbomachinery</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Nos</v>
+      </c>
+      <c r="E21">
+        <v>3800000</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F21"/>
   </ignoredErrors>
 </worksheet>
 </file>